--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/3. RACI Matrix_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/3. RACI Matrix_VNS.xlsx
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -507,6 +507,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -947,7 +950,7 @@
       <c r="A3" s="8" t="n"/>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>RACI Matrix – "VNS" – Custom University Learning Platform</t>
+          <t>RACI Matrix — "VNS" — Custom University Learning Platform</t>
         </is>
       </c>
       <c r="C3" s="38" t="n"/>
@@ -1076,67 +1079,66 @@
           <t>External Resources</t>
         </is>
       </c>
-      <c r="L6" s="42" t="n"/>
-      <c r="M6" s="42" t="n"/>
+      <c r="M6" s="10" t="n"/>
     </row>
     <row r="7" ht="75" customFormat="1" customHeight="1" s="15">
       <c r="A7" s="14" t="n"/>
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Project activity / deliverable</t>
+        </is>
+      </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Rector (Exec. Sponsor)</t>
+          <t>Lviv Polytechnic National University (Project Sponsor)</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Sponsor (LPNU)</t>
+          <t>Ministry of Education and Science (Sponsor, regulator)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Product Owner (K. Holovskyi)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (N. Zankovych)</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Business Analyst (A. Lysun)</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>Tech Lead / SWE (D. Lunhul)</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>DevOps / SWE (Y. Shevchuk)</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>QA / SWE (V. Kamelchuk)</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Customer (N. Boiko)</t>
+          <t>Technical Department of Lviv Polytechnic</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Tech Department</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
+          <t>End users — students and lecturers</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
       <c r="P7" s="14" t="n"/>
@@ -1188,7 +1190,7 @@
       <c r="J8" s="44" t="n"/>
       <c r="K8" s="44" t="n"/>
       <c r="L8" s="44" t="n"/>
-      <c r="M8" s="44" t="n"/>
+      <c r="M8" s="10" t="n"/>
       <c r="N8" s="10" t="n"/>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
@@ -1223,68 +1225,60 @@
       <c r="AS8" s="10" t="n"/>
       <c r="AT8" s="10" t="n"/>
     </row>
-    <row r="9" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="9" ht="40.5" customFormat="1" customHeight="1" s="19">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Audit the current VNS, agree the problem</t>
+          <t xml:space="preserve"> - Agree on the problem statement and business context (audit of the current VNS)</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
@@ -1319,68 +1313,56 @@
       <c r="AS9" s="10" t="n"/>
       <c r="AT9" s="10" t="n"/>
     </row>
-    <row r="10" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="10" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Identify and analyse stakeholders</t>
+          <t xml:space="preserve"> - Identify and analyse stakeholders (register, power/interest matrix)</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M10" s="10" t="n"/>
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="10" t="n"/>
       <c r="P10" s="10" t="n"/>
@@ -1415,68 +1397,60 @@
       <c r="AS10" s="10" t="n"/>
       <c r="AT10" s="10" t="n"/>
     </row>
-    <row r="11" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="11" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Choose a custom backend over Moodle</t>
+          <t xml:space="preserve"> - Approve the strategy: custom backend instead of Moodle integration</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M11" s="18" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
+      <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
       <c r="P11" s="10" t="n"/>
@@ -1511,68 +1485,60 @@
       <c r="AS11" s="10" t="n"/>
       <c r="AT11" s="10" t="n"/>
     </row>
-    <row r="12" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="12" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Develop the business case</t>
+          <t xml:space="preserve"> - Develop the business case and the success metrics</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
       <c r="O12" s="10" t="n"/>
       <c r="P12" s="10" t="n"/>
@@ -1607,11 +1573,11 @@
       <c r="AS12" s="10" t="n"/>
       <c r="AT12" s="10" t="n"/>
     </row>
-    <row r="13" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="13" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Approve the project charter and MVP scope</t>
+          <t xml:space="preserve"> - Approve the project charter and the MVP scope</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -1654,21 +1620,13 @@
           <t>I</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K13" s="17" t="n"/>
       <c r="L13" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
@@ -1707,7 +1665,7 @@
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Planing Phase</t>
+          <t>Planning Phase</t>
         </is>
       </c>
       <c r="C14" s="35" t="n"/>
@@ -1720,7 +1678,7 @@
       <c r="J14" s="44" t="n"/>
       <c r="K14" s="44" t="n"/>
       <c r="L14" s="44" t="n"/>
-      <c r="M14" s="44" t="n"/>
+      <c r="M14" s="10" t="n"/>
       <c r="N14" s="10" t="n"/>
       <c r="O14" s="10" t="n"/>
       <c r="P14" s="10" t="n"/>
@@ -1755,19 +1713,19 @@
       <c r="AS14" s="10" t="n"/>
       <c r="AT14" s="10" t="n"/>
     </row>
-    <row r="15" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="15" ht="40.5" customFormat="1" customHeight="1" s="19">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Elicit requirements and build UML models</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="inlineStr">
+          <t xml:space="preserve"> - Elicit and document requirements (interviews with lecturers, student surveys)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
+      <c r="D15" s="18" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>C</t>
@@ -1775,7 +1733,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -1798,21 +1756,13 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K15" s="17" t="n"/>
       <c r="L15" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
@@ -1847,42 +1797,38 @@
       <c r="AS15" s="10" t="n"/>
       <c r="AT15" s="10" t="n"/>
     </row>
-    <row r="16" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="16" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Design the data model and architecture</t>
+          <t xml:space="preserve"> - Build UML models (use case, activity) for the product scenarios</t>
         </is>
       </c>
       <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R/A</t>
         </is>
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>R/A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="J16" s="18" t="inlineStr">
@@ -1890,17 +1836,13 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="n"/>
+      <c r="M16" s="10" t="n"/>
       <c r="N16" s="10" t="n"/>
       <c r="O16" s="10" t="n"/>
       <c r="P16" s="10" t="n"/>
@@ -1935,33 +1877,25 @@
       <c r="AS16" s="10" t="n"/>
       <c r="AT16" s="10" t="n"/>
     </row>
-    <row r="17" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="17" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Select the tech stack and LLM API provider</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
+          <t xml:space="preserve"> - Design the data model and the custom backend architecture</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
           <t>C</t>
@@ -1969,7 +1903,7 @@
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R/A</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -1982,17 +1916,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M17" s="18" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
       <c r="P17" s="10" t="n"/>
@@ -2027,21 +1953,21 @@
       <c r="AS17" s="10" t="n"/>
       <c r="AT17" s="10" t="n"/>
     </row>
-    <row r="18" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="18" ht="40.5" customFormat="1" customHeight="1" s="19">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Approve student data use and LLM API access</t>
+          <t xml:space="preserve"> - Approve processing of student personal data and transfer of materials to the LLM API</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2066,7 +1992,7 @@
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="J18" s="18" t="inlineStr">
@@ -2076,19 +2002,15 @@
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
+      <c r="M18" s="10" t="n"/>
       <c r="N18" s="10" t="n"/>
       <c r="O18" s="10" t="n"/>
       <c r="P18" s="10" t="n"/>
@@ -2123,68 +2045,52 @@
       <c r="AS18" s="10" t="n"/>
       <c r="AT18" s="10" t="n"/>
     </row>
-    <row r="19" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="19" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Create the schedule and communication plan</t>
+          <t xml:space="preserve"> - Produce the communications plan and the project schedule</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
@@ -2219,24 +2125,52 @@
       <c r="AS19" s="10" t="n"/>
       <c r="AT19" s="10" t="n"/>
     </row>
-    <row r="20" ht="16.9" customFormat="1" customHeight="1" s="19">
+    <row r="20" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A20" s="10" t="n"/>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Execution Phase</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="44" t="n"/>
-      <c r="L20" s="44" t="n"/>
-      <c r="M20" s="44" t="n"/>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Select the technology stack and the LLM API provider</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
@@ -2271,64 +2205,24 @@
       <c r="AS20" s="10" t="n"/>
       <c r="AT20" s="10" t="n"/>
     </row>
-    <row r="21" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="21" ht="16.9" customFormat="1" customHeight="1" s="19">
       <c r="A21" s="10" t="n"/>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Registration via the student registry</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Execution Phase</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="44" t="n"/>
+      <c r="I21" s="44" t="n"/>
+      <c r="J21" s="44" t="n"/>
+      <c r="K21" s="44" t="n"/>
+      <c r="L21" s="44" t="n"/>
+      <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
@@ -2363,64 +2257,60 @@
       <c r="AS21" s="10" t="n"/>
       <c r="AT21" s="10" t="n"/>
     </row>
-    <row r="22" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="22" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Courses, deadlines, grade forecast</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="inlineStr">
+          <t xml:space="preserve"> - Obtain the student registry; implement registration and authentication</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M22" s="10" t="n"/>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="10" t="n"/>
@@ -2455,29 +2345,25 @@
       <c r="AS22" s="10" t="n"/>
       <c r="AT22" s="10" t="n"/>
     </row>
-    <row r="23" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="23" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Communication hub and Study Spaces</t>
+          <t xml:space="preserve"> - Implement courses, materials, deadlines and grade forecasting</t>
         </is>
       </c>
       <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
           <t>C</t>
@@ -2495,24 +2381,16 @@
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n"/>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="10" t="n"/>
@@ -2547,29 +2425,25 @@
       <c r="AS23" s="10" t="n"/>
       <c r="AT23" s="10" t="n"/>
     </row>
-    <row r="24" ht="15.75" customFormat="1" customHeight="1" s="19">
+    <row r="24" ht="28" customFormat="1" customHeight="1" s="19">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - AI assistant: summaries, quizzes, Q&amp;A</t>
+          <t xml:space="preserve"> - Implement the communication hub and Study Spaces</t>
         </is>
       </c>
       <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
           <t>C</t>
@@ -2577,34 +2451,26 @@
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K24" s="17" t="n"/>
       <c r="L24" s="18" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="n"/>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
@@ -2639,46 +2505,46 @@
       <c r="AS24" s="10" t="n"/>
       <c r="AT24" s="10" t="n"/>
     </row>
-    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="25" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Environments and CI/CD</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="inlineStr">
+          <t xml:space="preserve"> - Implement the AI assistant: summaries, quizzes, “Ask the course”</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
+      <c r="D25" s="18" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>R/A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="K25" s="17" t="n"/>
@@ -2687,51 +2553,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="M25" s="18" t="n"/>
+      <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
     </row>
-    <row r="26" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="26" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Testing and acceptance checks</t>
+          <t xml:space="preserve"> - Set up environments and configure CI/CD</t>
         </is>
       </c>
       <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="n"/>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>R/A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -2739,45 +2597,65 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="10" t="n"/>
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
     </row>
-    <row r="27" ht="16.9" customFormat="1" customHeight="1" s="7">
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Control Phase</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="n"/>
-      <c r="D27" s="44" t="n"/>
-      <c r="E27" s="44" t="n"/>
-      <c r="F27" s="44" t="n"/>
-      <c r="G27" s="44" t="n"/>
-      <c r="H27" s="44" t="n"/>
-      <c r="I27" s="44" t="n"/>
-      <c r="J27" s="44" t="n"/>
-      <c r="K27" s="44" t="n"/>
-      <c r="L27" s="44" t="n"/>
-      <c r="M27" s="44" t="n"/>
+    <row r="27" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Run testing and acceptance checks</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
     </row>
-    <row r="28" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="28" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Manage scope changes and backlog</t>
+          <t xml:space="preserve"> - Deploy the platform to the production environment</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -2785,463 +2663,525 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="D28" s="18" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="n"/>
       <c r="O28" s="10" t="n"/>
       <c r="P28" s="10" t="n"/>
     </row>
-    <row r="29" ht="15.75" customFormat="1" customHeight="1" s="7">
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Monitor LLM API costs and quotas</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="17" t="n"/>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="n"/>
+    <row r="29" ht="16.9" customFormat="1" customHeight="1" s="7">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Control Phase</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="44" t="n"/>
+      <c r="H29" s="44" t="n"/>
+      <c r="I29" s="44" t="n"/>
+      <c r="J29" s="44" t="n"/>
+      <c r="K29" s="44" t="n"/>
+      <c r="L29" s="44" t="n"/>
+      <c r="M29" s="10" t="n"/>
       <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
       <c r="P29" s="10" t="n"/>
     </row>
-    <row r="30" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="30" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Report status to sponsors</t>
+          <t xml:space="preserve"> - Manage scope changes and backlog priorities</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="18" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L30" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M30" s="10" t="n"/>
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
     </row>
-    <row r="31" ht="16.9" customFormat="1" customHeight="1" s="7">
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Close Phase</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="44" t="n"/>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="44" t="n"/>
-      <c r="H31" s="44" t="n"/>
-      <c r="I31" s="44" t="n"/>
-      <c r="J31" s="44" t="n"/>
-      <c r="K31" s="44" t="n"/>
-      <c r="L31" s="44" t="n"/>
-      <c r="M31" s="44" t="n"/>
+    <row r="31" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Control quality, defects and adherence to the acceptance criteria</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
     </row>
-    <row r="32" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="32" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Run the student pilot, collect feedback</t>
+          <t xml:space="preserve"> - Monitor LLM API costs, quotas and request limits</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M32" s="18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="17" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="10" t="n"/>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
     </row>
-    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="7">
+    <row r="33" ht="28" customFormat="1" customHeight="1" s="7">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Hand over the system and documentation</t>
+          <t xml:space="preserve"> - Report project status to the sponsors</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M33" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
     </row>
-    <row r="34" ht="15.75" customFormat="1" customHeight="1" s="7">
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - Capture lessons learned, close project</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H34" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J34" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L34" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+    <row r="34" ht="16.9" customFormat="1" customHeight="1" s="7">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Close Phase</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="44" t="n"/>
+      <c r="F34" s="44" t="n"/>
+      <c r="G34" s="44" t="n"/>
+      <c r="H34" s="44" t="n"/>
+      <c r="I34" s="44" t="n"/>
+      <c r="J34" s="44" t="n"/>
+      <c r="K34" s="44" t="n"/>
+      <c r="L34" s="44" t="n"/>
+      <c r="M34" s="10" t="n"/>
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
     </row>
-    <row r="35" customFormat="1" s="7">
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-    </row>
-    <row r="36" customFormat="1" s="7">
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-    </row>
-    <row r="37" customFormat="1" s="7">
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
+    <row r="35" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Run the pilot with students and lecturers and collect feedback</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Hand over the system and documentation to the sponsor</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L36" s="18" t="n"/>
+      <c r="M36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Capture lessons learned and close the project</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="10" t="n"/>
     </row>
     <row r="38" customFormat="1" s="7">
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
     </row>
     <row r="39" customFormat="1" s="7">
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
     </row>
     <row r="40" customFormat="1" s="7">
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="10" t="n"/>
     </row>
     <row r="41" customFormat="1" s="7">
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
     </row>
     <row r="42" customFormat="1" s="7">
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
     </row>
     <row r="43" customFormat="1" s="7">
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
     </row>
     <row r="44" customFormat="1" s="7">
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
     </row>
     <row r="45" customFormat="1" s="7">
       <c r="B45" s="5" t="n"/>
@@ -5044,16 +4984,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="F6:H6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="C27:M27"/>
-    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="C8:L8"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C8:M8"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="B3:M4"/>
-    <mergeCell ref="C31:M31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5075,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="13.15"/>
   <cols>
     <col width="79.28515625" customWidth="1" min="1" max="1"/>
@@ -5084,26 +5024,165 @@
     <row r="1" ht="20.25" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>Instructional Notes for the RACI Matrix:</t>
-        </is>
-      </c>
-    </row>
+          <t>Instructional Notes for the RACI Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="240.75" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>The RACI Matrix is a powerful tool to assist in the identification of roles and assigning of cross-functional responsibilities to a project deliverable or activity.  
-RACI represents:  R - Responsibility, A - Accountable, C - Consulted, and I - Informed
-RACI Definitions:
-Responsible: People or stakeholders who do the work. They must complete the task or objective or make the decision. Several people can be jointly Responsible.
-Accountable: Person or stakeholder who is the “owner” of the work. He or she must sign off or approve when the task, objective or decision is complete. This person must make sure that responsibilities are assigned in the matrix for all related activities. Success requires that there is only one person Accountable, which means that “the buck stops there.”
-Consulted: People or stakeholders who need to give input before the work can be done and signed-off on. These people are “in the loop” and active participants.
-Informed: People or stakeholders who need to be kept “in the picture.” They need updates on progress or decisions, but they do not need to be formally consulted, nor do they contribute directly to the task or decision.</t>
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>The RACI Matrix is a tool to assist in the identification of roles and the assigning of cross-functional responsibilities to a project deliverable or activity. It removes the situation where an activity is formally in the plan but no role treats it as their own.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16.9" customHeight="1">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>RACI represents: R - Responsibility, A - Accountable, C - Consulted, and I - Informed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>Responsible: People or stakeholders who do the work. They must complete the task or objective or make the decision. Several people can be jointly Responsible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Accountable: Person or stakeholder who is the owner of the work. He or she must sign off or approve when the task, objective or decision is complete, and must make sure that responsibilities are assigned for all related activities. Success requires that there is only one person Accountable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Consulted: People or stakeholders who need to give input before the work can be done and signed off. These people are in the loop and are active participants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Informed: People or stakeholders who need to be kept in the picture. They need updates on progress or decisions, but they are not formally consulted and do not contribute directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Rules applied in this matrix:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Every row has exactly one role marked Accountable (counting the R/A combination).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Every row has at least one Responsible role, otherwise nobody would perform the activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. An empty cell means the role is not involved in that activity. This is a deliberate decision, not an omission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. The number of Consulted and Informed marks is kept moderate: too many C slows the work down, too many I turns communication into noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Only roles with high influence in the Stakeholder Register are ever Accountable. Low-influence roles (DevOps, QA, the Technical Department, end users) can be Responsible or Consulted, but never sign off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Tech Lead, DevOps and QA are all software engineers (SWE), so all three are Responsible for implementing the product modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Relationship to the other artifacts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The roles in the columns correspond to the entries in “1. Stakeholder Register_VNS.xlsx”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Stakeholders marked Key Player in the register hold A or R in the key phases of this matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Stakeholders with low interest (the Ministry, the Project Manager, the Technical Department) are consulted only on decisions that concern them and are otherwise informed or not involved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The frequency and format of interaction for roles holding A, R or C are detailed in “4. Communication Plan_VNS.xlsx”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>Demonstration note: this is a training business case. The university stakeholders named here are addressed in a demonstration context and no real agreements have been concluded with them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
